--- a/data/demo_data/football/map-football.xlsx
+++ b/data/demo_data/football/map-football.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\demo_data\football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B2BB7A-9A6E-468B-80B6-434F595C7069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0486513-9C4D-406D-8731-CD57D744D175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BEEE0838-8381-44BA-9592-E3BE3FB7B4F4}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{BEEE0838-8381-44BA-9592-E3BE3FB7B4F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Key</t>
   </si>
@@ -75,34 +75,31 @@
     <t>Minutes</t>
   </si>
   <si>
-    <t>non-penalty expected goals</t>
-  </si>
-  <si>
-    <t>goals</t>
-  </si>
-  <si>
-    <t>smart passes</t>
-  </si>
-  <si>
-    <t>air duels</t>
-  </si>
-  <si>
-    <t>ground duels</t>
-  </si>
-  <si>
-    <t>final third passes</t>
-  </si>
-  <si>
-    <t>final third receptions</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>assits</t>
-  </si>
-  <si>
-    <t>key</t>
+    <t>non-penalty expected goals adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>final third receptions adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>ground duels won adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>air duels won adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>smart passes adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>final third passes adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>goals adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>assits adjusted per 90 minutes</t>
+  </si>
+  <si>
+    <t>key passes adjusted per 90 minutes</t>
   </si>
 </sst>
 </file>
@@ -458,7 +455,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.08984375" customWidth="1"/>
-    <col min="2" max="2" width="32.6328125" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -490,7 +487,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -498,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -514,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -522,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -530,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -538,7 +535,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -546,7 +543,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
